--- a/rtss-pre1917/src/main/resources/csk-dvizhenie-evropriskoi-chasti-rossii/year-volumes/1881.xlsx
+++ b/rtss-pre1917/src/main/resources/csk-dvizhenie-evropriskoi-chasti-rossii/year-volumes/1881.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\csk-dvizhenie-evropriskoi-chasti-rossii\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A64174-8D28-43DA-B339-5A2111B3D1CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45F9DD35-5A4A-462C-B0DE-7429387581E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="1881" sheetId="1" r:id="rId1"/>
-    <sheet name="notes" sheetId="2" r:id="rId2"/>
+    <sheet name="notes" sheetId="2" r:id="rId1"/>
+    <sheet name="1881" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -589,6 +589,84 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="90" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -2970,84 +3048,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
-  <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="90" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{0cf7ac0a-4681-4823-ab0b-04ef02c5f873}" enabled="1" method="Standard" siteId="{42f7676c-f455-423c-82f6-dc2d99791af7}" contentBits="0" removed="0"/>

--- a/rtss-pre1917/src/main/resources/csk-dvizhenie-evropriskoi-chasti-rossii/year-volumes/1881.xlsx
+++ b/rtss-pre1917/src/main/resources/csk-dvizhenie-evropriskoi-chasti-rossii/year-volumes/1881.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\csk-dvizhenie-evropriskoi-chasti-rossii\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45F9DD35-5A4A-462C-B0DE-7429387581E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A227C2E9-1CC6-44EB-8852-3553F9129099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -283,7 +283,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -295,6 +295,11 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Carlito"/>
       <family val="2"/>
@@ -360,15 +365,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -377,6 +373,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -700,22 +705,22 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="M1" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="11" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2970,31 +2975,31 @@
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="9" t="s">
+      <c r="A52" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B52" s="10">
+      <c r="B52" s="13">
         <v>1887462</v>
       </c>
-      <c r="C52" s="10">
+      <c r="C52" s="13">
         <v>1792232</v>
       </c>
-      <c r="D52" s="10">
+      <c r="D52" s="13">
         <v>3679694</v>
       </c>
-      <c r="E52" s="10">
+      <c r="E52" s="13">
         <v>1328757</v>
       </c>
-      <c r="F52" s="10">
+      <c r="F52" s="13">
         <v>1231726</v>
       </c>
-      <c r="G52" s="10">
+      <c r="G52" s="13">
         <v>2560483</v>
       </c>
-      <c r="H52" s="11">
+      <c r="H52" s="14">
         <v>105.3</v>
       </c>
-      <c r="I52" s="11">
+      <c r="I52" s="14">
         <v>140.30000000000001</v>
       </c>
       <c r="K52" s="2">
@@ -3015,7 +3020,7 @@
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="12" t="s">
+      <c r="A54" s="9" t="s">
         <v>73</v>
       </c>
       <c r="B54" s="2">
